--- a/artfynd/A 53048-2025 artfynd.xlsx
+++ b/artfynd/A 53048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224139</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129224137</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129224138</v>
       </c>
       <c r="B4" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129224136</v>
       </c>
       <c r="B5" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129224140</v>
       </c>
       <c r="B6" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129224141</v>
       </c>
       <c r="B7" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53048-2025 artfynd.xlsx
+++ b/artfynd/A 53048-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>129224136</v>
       </c>
       <c r="B5" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129224140</v>
       </c>
       <c r="B6" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129224141</v>
       </c>
       <c r="B7" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53048-2025 artfynd.xlsx
+++ b/artfynd/A 53048-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224139</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129224137</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129224138</v>
       </c>
       <c r="B4" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129224136</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129224140</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129224141</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53048-2025 artfynd.xlsx
+++ b/artfynd/A 53048-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129224139</v>
+        <v>129224137</v>
       </c>
       <c r="B2" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575300</v>
+        <v>575298</v>
       </c>
       <c r="R2" t="n">
-        <v>6653943</v>
+        <v>6653734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129224137</v>
+        <v>129224138</v>
       </c>
       <c r="B3" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575298</v>
+        <v>575313</v>
       </c>
       <c r="R3" t="n">
-        <v>6653734</v>
+        <v>6653816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129224138</v>
+        <v>129224139</v>
       </c>
       <c r="B4" t="n">
-        <v>92901</v>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575313</v>
+        <v>575300</v>
       </c>
       <c r="R4" t="n">
-        <v>6653816</v>
+        <v>6653943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>129224136</v>
       </c>
       <c r="B5" t="n">
-        <v>97633</v>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>129224140</v>
       </c>
       <c r="B6" t="n">
-        <v>97633</v>
+        <v>97989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>129224141</v>
       </c>
       <c r="B7" t="n">
-        <v>97633</v>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53048-2025 artfynd.xlsx
+++ b/artfynd/A 53048-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224139</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224136</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224140</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,8 +1338,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>